--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_386_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_386_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>7</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>13</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>15</v>
       </c>
       <c r="T17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>4</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>40:32</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,22 +1451,22 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>33:30</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -1727,16 +1727,16 @@
         <v>22</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>3</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>45:30</t>
+          <t>25:31</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
     </row>
@@ -1923,10 +1923,10 @@
         <v>14</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>35:57</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,22 +2039,22 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
         <v>15</v>
       </c>
       <c r="T21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>45:15</t>
+          <t>25:16</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
     </row>
@@ -2318,13 +2318,13 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>4</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>34:29</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>40.6%</t>
         </is>
       </c>
     </row>
@@ -2511,16 +2511,16 @@
         <v>9</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>3</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>38:14</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
     </row>
@@ -2707,10 +2707,10 @@
         <v>8</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>35:13</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,22 +2823,22 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>23.8%</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>02:47</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>41:15</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,22 +3411,22 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>15.5%</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>32:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AN28" t="n">
@@ -3607,17 +3607,17 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
@@ -3827,16 +3827,16 @@
         <v>112</v>
       </c>
       <c r="T30" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>33</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>58:19</t>
+          <t>28:19</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>49.3%</t>
         </is>
       </c>
     </row>
@@ -4684,16 +4684,16 @@
         <v>20</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>4</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>48:29</t>
+          <t>28:29</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>30:38</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>04:13</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>51:10</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,12 +5388,12 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>30:33</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
@@ -5866,10 +5866,10 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>4</v>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>39:42</t>
+          <t>29:43</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,22 +5976,22 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
         <v>4</v>
       </c>
       <c r="T44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>42:21</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>6.8%</t>
         </is>
       </c>
     </row>
@@ -6255,13 +6255,13 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>9</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>59:19</t>
+          <t>29:20</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
@@ -6784,16 +6784,16 @@
         <v>98</v>
       </c>
       <c r="T48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>22</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_386_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_386_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M2" t="n">
         <v>7</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M3" t="n">
         <v>13</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>15</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
         <v>4</v>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1727,16 +1727,16 @@
         <v>22</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>3</v>
@@ -1923,10 +1923,10 @@
         <v>14</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
         <v>15</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2318,13 +2318,13 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X22" t="n">
         <v>4</v>
@@ -2511,16 +2511,16 @@
         <v>9</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>3</v>
@@ -2707,10 +2707,10 @@
         <v>8</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>112</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X30" t="n">
         <v>33</v>
@@ -4684,16 +4684,16 @@
         <v>20</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X37" t="n">
         <v>4</v>
@@ -5866,10 +5866,10 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X43" t="n">
         <v>4</v>
@@ -6056,7 +6056,7 @@
         <v>4</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -6255,13 +6255,13 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
         <v>9</v>
@@ -6784,16 +6784,16 @@
         <v>98</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X48" t="n">
         <v>22</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_386_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_386_EL.xlsx
@@ -674,10 +674,10 @@
         <v>7</v>
       </c>
       <c r="N2" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="P2" t="n">
         <v>6</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>78.95</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1739,14 +1739,14 @@
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -2131,10 +2131,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
         <v>2</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -3503,14 +3503,14 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>6</v>
       </c>
       <c r="X30" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="Y30" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4500,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4696,10 +4696,10 @@
         <v>4</v>
       </c>
       <c r="X37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -5872,14 +5872,14 @@
         <v>3</v>
       </c>
       <c r="X43" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y43" t="n">
         <v>4</v>
       </c>
-      <c r="Y43" t="n">
-        <v>5</v>
-      </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6264,10 +6264,10 @@
         <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y45" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>8</v>
       </c>
       <c r="X48" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="Y48" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="AA48" t="n">
